--- a/用卷/2010.xlsx
+++ b/用卷/2010.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0E7EB1-BD1B-41F6-A454-86F71994BF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5898FE5F-C946-436E-825D-F752E2317002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -993,7 +993,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
